--- a/customer_service_agent_forms/018_customer_service_form--customer_service_agent_forms.xlsx
+++ b/customer_service_agent_forms/018_customer_service_form--customer_service_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Customer Message</t>
+          <t>Customer Form Message</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Customer Form Submit Date</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Customer Form Submit Time</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Customer Form Submit Notes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'save_draft'}</t>
+          <t>save_draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Save Draft'}</t>
+          <t>Save Draft</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cancel_form'}</t>
+          <t>cancel_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel Form'}</t>
+          <t>Cancel Form</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'save_draft'}</t>
+          <t>save_draft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Save Draft'}</t>
+          <t>Save Draft</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'cancel_form'}</t>
+          <t>cancel_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel Form'}</t>
+          <t>Cancel Form</t>
         </is>
       </c>
     </row>
